--- a/output/tables/QC/finished_tables/Significant_null_alleles.xlsx
+++ b/output/tables/QC/finished_tables/Significant_null_alleles.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\R_WD\revised_bison_popgen\output\tables\QC\finished_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF0162C-D190-451F-99F9-AD8A4AE5EDFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B170A3F4-E603-4C6F-8378-287E98F3E7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="20343" windowHeight="12934" xr2:uid="{534F6629-D209-43AE-8C7A-A28B3D8C9AD8}"/>
   </bookViews>
@@ -188,6 +188,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -693,31 +696,32 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1098,1003 +1102,1004 @@
   <dimension ref="A1:E71"/>
   <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="10.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="3"/>
+    <col min="6" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="6">
         <v>0.10566</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="6">
         <v>0.16298000000000001</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="C4" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="8">
         <v>0.15257000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="6">
         <v>0.11065</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="9">
+      <c r="C6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="6">
         <v>0.14379</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="C7" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="8">
         <v>0.11928999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="9">
+      <c r="C8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="6">
         <v>0.1129</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="9">
+      <c r="C9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="6">
         <v>0.1207</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="C10" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="8">
         <v>0.11097</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="2">
+      <c r="C11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="8">
         <v>0.15257000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="6">
         <v>0.20821999999999999</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="9">
+      <c r="C13" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="6">
         <v>0.12162000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="2">
+      <c r="C14" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="8">
         <v>0.16408</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="8">
         <v>0.11065</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="9">
+      <c r="C16" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="6">
         <v>0.14584</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="8">
         <v>0.13200999999999999</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="9">
+      <c r="C18" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="6">
         <v>0.16344</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="6">
         <v>0.26895000000000002</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="2">
+      <c r="C20" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="8">
         <v>0.10813</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="8">
         <v>0.19830999999999999</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="9">
+      <c r="C22" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="6">
         <v>0.11922000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="8">
         <v>0.23618</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="8">
         <v>0.18776999999999999</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="8">
         <v>0.11006000000000001</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="8">
         <v>0.16486999999999999</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="6">
         <v>0.18067</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="6">
         <v>0.11065</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="9">
+      <c r="C29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="6">
         <v>0.15257000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="2">
+      <c r="C30" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="8">
         <v>0.10018000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="9">
+      <c r="C31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="6">
         <v>0.16177</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="6">
         <v>0.10478999999999999</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" s="9">
+      <c r="C33" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="6">
         <v>0.14152999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="9">
+      <c r="C34" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="6">
         <v>0.10732999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D35" s="2">
+      <c r="C35" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="8">
         <v>0.18936</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="8">
         <v>0.17976</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="6">
         <v>0.15742999999999999</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="6">
         <v>0.12271</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D39" s="9">
+      <c r="C39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="6">
         <v>0.29028999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40" s="2">
+      <c r="C40" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="8">
         <v>0.14507999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="8">
         <v>0.20666999999999999</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="8">
         <v>0.11752</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="8">
         <v>0.11027000000000001</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D44" s="2">
+      <c r="C44" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="8">
         <v>0.11131000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="6">
         <v>0.11989</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" s="9">
+      <c r="C46" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" s="6">
         <v>0.126</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47" s="6">
         <v>0.14613999999999999</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="6">
         <v>0.13086</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="D48" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D49" s="9">
+      <c r="C49" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49" s="6">
         <v>0.19664999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="8">
         <v>0.19170000000000001</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="8">
         <v>0.11928</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D52" s="2">
+      <c r="C52" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D52" s="8">
         <v>0.19664999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C53" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D53" s="9">
+      <c r="C53" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="6">
         <v>0.19466</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D54" s="9">
+      <c r="C54" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D54" s="6">
         <v>0.10599</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C55" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D55" s="9">
+      <c r="C55" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D55" s="6">
         <v>0.19664999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="8">
         <v>0.23618</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C57" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D57" s="9">
+      <c r="C57" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D57" s="6">
         <v>0.13167000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C58" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D58" s="9">
+      <c r="C58" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D58" s="6">
         <v>0.11323</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D59" s="2">
+      <c r="C59" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D59" s="8">
         <v>0.10688</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D60" s="9">
+      <c r="C60" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D60" s="6">
         <v>0.23296</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C61" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D61" s="9">
+      <c r="C61" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D61" s="6">
         <v>0.20152999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C62" s="9">
+      <c r="C62" s="6">
         <v>0.15651999999999999</v>
       </c>
-      <c r="D62" s="9" t="s">
+      <c r="D62" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D63" s="2">
+      <c r="C63" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D63" s="8">
         <v>0.10757</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D64" s="2">
+      <c r="C64" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D64" s="8">
         <v>0.16056000000000001</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C65" s="9">
+      <c r="C65" s="6">
         <v>0.12037</v>
       </c>
-      <c r="D65" s="9">
+      <c r="D65" s="6">
         <v>0.14254</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C66" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D66" s="9">
+      <c r="C66" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D66" s="6">
         <v>0.10356</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C67" s="9">
+      <c r="C67" s="6">
         <v>0.16278000000000001</v>
       </c>
-      <c r="D67" s="9" t="s">
+      <c r="D67" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D68" s="2">
+      <c r="C68" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D68" s="8">
         <v>0.12447999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C69" s="2">
+      <c r="C69" s="8">
         <v>0.19830999999999999</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D69" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C70" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D70" s="9">
+      <c r="C70" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D70" s="6">
         <v>0.24709</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C71" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D71" s="7">
+      <c r="C71" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D71" s="10">
         <v>0.16408</v>
       </c>
     </row>
